--- a/inst/resources/outputs_schema_data_analytics_fsl_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_fsl_template.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
